--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79539</v>
+        <v>79543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79543</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105486</v>
+        <v>105488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79554</v>
+        <v>79646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,14 +873,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,14 +974,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,14 +1080,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,14 +1189,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105508</v>
+        <v>105695</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,14 +1290,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1391,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79646</v>
+        <v>79650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>79555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79560</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127467598</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127467600</v>
       </c>
       <c r="B3" t="n">
-        <v>79569</v>
+        <v>79570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127467597</v>
       </c>
       <c r="B2" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>127467605</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127467606</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>127467610</v>
       </c>
       <c r="B7" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>127467596</v>
       </c>
       <c r="B8" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127467597</v>
+        <v>127467596</v>
       </c>
       <c r="B2" t="n">
-        <v>91549</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775524</v>
+        <v>775582</v>
       </c>
       <c r="R2" t="n">
-        <v>7189810</v>
+        <v>7189802</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127467600</v>
+        <v>127467597</v>
       </c>
       <c r="B3" t="n">
-        <v>79570</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229830</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Klutmark, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775535</v>
+        <v>775524</v>
       </c>
       <c r="R3" t="n">
-        <v>7189825</v>
+        <v>7189810</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,9 +853,8 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,45 +877,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127467605</v>
+        <v>127467602</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Klutmark, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775582</v>
+        <v>775633</v>
       </c>
       <c r="R4" t="n">
-        <v>7189966</v>
+        <v>7189865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +956,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,45 +991,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127467606</v>
+        <v>127467598</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Klutmark, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775621</v>
+        <v>775578</v>
       </c>
       <c r="R5" t="n">
-        <v>7189940</v>
+        <v>7189963</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,11 +1070,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bild 2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,53 +1100,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127467598</v>
+        <v>127467605</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klutmark, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775578</v>
+        <v>775582</v>
       </c>
       <c r="R6" t="n">
-        <v>7189963</v>
+        <v>7189966</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,32 +1201,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127467610</v>
+        <v>127467606</v>
       </c>
       <c r="B7" t="n">
-        <v>105780</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775578</v>
+        <v>775621</v>
       </c>
       <c r="R7" t="n">
-        <v>7189971</v>
+        <v>7189940</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,6 +1272,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127467596</v>
+        <v>127467607</v>
       </c>
       <c r="B8" t="n">
-        <v>91549</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775582</v>
+        <v>775628</v>
       </c>
       <c r="R8" t="n">
-        <v>7189802</v>
+        <v>7189889</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1401,212 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127467610</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Klutmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>775578</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7189971</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127467600</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79853</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Klutmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>775535</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7189825</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 32739-2025 artfynd.xlsx
+++ b/artfynd/A 32739-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467596</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467597</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467602</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467605</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467607</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467610</t>
         </is>
       </c>
     </row>
@@ -1611,8 +1656,24 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127467600</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>